--- a/.cursor/scratch/tax_turbo_parts/INFLOW_LEDGER.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/INFLOW_LEDGER.xlsx
@@ -53,12 +53,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -452,30 +452,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="78" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>2025 checking inflows — JSC 9922 + joint 0203 (folder 07) — not tax advice</t>
+          <t>2025 checking inflows after 2026-09-18 answers — JSC 9922 + joint 0203 — not tax advice</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Cash-basis by deposit date. BOM → Consultant. JAKE C / SEFOF → reimbursement EXCLUDED. Delach / Ava / Joan → 216 Oak Park STR / RENTAL INCOME. Bear Creek + UTMA Thomas wires → not income. Hindman/Freeman payroll stays on the W-2 tab. EPGC Mercury ACH into 9922 is a transfer, not income.</t>
+          <t>Cash-basis by deposit date. GCM BOM → personal 1099 / GCM tab (NOT EPGC Consultant). JAKE C / SEFOF → reimbursement EXCLUDED (May 22 CONFIRMED). Delach + Ava (co-tenant CONFIRMED) + Joan → 216 Oak Park STR / RENTAL INCOME. Bear Creek = gift to Jake from parents. UTMA Thomas $5k each excluded. Freeman’s Sale 6428 $11,000 → Art Sales (check to Megan). 8507 Zelle OUT Joan $675 → 216 INTERIOR MAINTENANCE.</t>
         </is>
       </c>
     </row>
@@ -563,42 +563,42 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>0203 joint</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>AVA L HERNANDEZ</t>
         </is>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="D6" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>STR / RENTAL INCOME</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>216 N. Oak Park Ave</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>APPLIED-YELLOW</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>Rent (same day as Delach). Roommate/co-tenant? ASK</t>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>APPLIED</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Rent (same day as Delach). Delach co-tenant CONFIRMED.</t>
         </is>
       </c>
     </row>
@@ -643,42 +643,42 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>0203 joint</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>2025-02-28</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>AVA L HERNANDEZ</t>
         </is>
       </c>
-      <c r="D8" s="7" t="n">
+      <c r="D8" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>STR / RENTAL INCOME</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>216 N. Oak Park Ave</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>APPLIED-YELLOW</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>Rent. Roommate/co-tenant? ASK</t>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>APPLIED</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Rent. Delach co-tenant CONFIRMED.</t>
         </is>
       </c>
     </row>
@@ -723,82 +723,82 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>0203 joint</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>AVA L HERNANDEZ</t>
         </is>
       </c>
-      <c r="D10" s="7" t="n">
+      <c r="D10" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>STR / RENTAL INCOME</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>216 N. Oak Park Ave</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>APPLIED-YELLOW</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>April Rent. Roommate/co-tenant? ASK</t>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>APPLIED</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>April Rent. Delach co-tenant CONFIRMED.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>0203 joint</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>2025-04-28</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>AVA L HERNANDEZ</t>
         </is>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D11" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>STR / RENTAL INCOME</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>216 N. Oak Park Ave</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>APPLIED-YELLOW</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>May Rent. Roommate/co-tenant? ASK</t>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>APPLIED</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>May Rent. Delach co-tenant CONFIRMED.</t>
         </is>
       </c>
     </row>
@@ -883,82 +883,82 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>0203 joint</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>2025-05-30</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>AVA L HERNANDEZ</t>
         </is>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="D14" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>STR / RENTAL INCOME</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>216 N. Oak Park Ave</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>APPLIED-YELLOW</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>June rent. Roommate/co-tenant? ASK</t>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>APPLIED</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>June rent. Delach co-tenant CONFIRMED.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>0203 joint</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>2025-06-23</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>AVA L HERNANDEZ</t>
         </is>
       </c>
-      <c r="D15" s="7" t="n">
+      <c r="D15" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>STR / RENTAL INCOME</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>216 N. Oak Park Ave</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>APPLIED-YELLOW</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>july rent. Roommate/co-tenant? ASK</t>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>APPLIED</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>july rent. Delach co-tenant CONFIRMED.</t>
         </is>
       </c>
     </row>
@@ -1043,42 +1043,42 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>0203 joint</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>AVA L HERNANDEZ</t>
         </is>
       </c>
-      <c r="D18" s="7" t="n">
+      <c r="D18" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>STR / RENTAL INCOME</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>216 N. Oak Park Ave</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>APPLIED-YELLOW</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>August rent. Roommate/co-tenant? ASK</t>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>APPLIED</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>August rent. Delach co-tenant CONFIRMED.</t>
         </is>
       </c>
     </row>
@@ -1123,122 +1123,122 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>0203 joint</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>AVA L HERNANDEZ</t>
         </is>
       </c>
-      <c r="D20" s="7" t="n">
+      <c r="D20" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>STR / RENTAL INCOME</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>216 N. Oak Park Ave</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>APPLIED-YELLOW</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>september rent. Roommate/co-tenant? ASK</t>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>APPLIED</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>september rent. Delach co-tenant CONFIRMED.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>0203 joint</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>2025-12-01</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>JOAN FRIEDBERGER</t>
         </is>
       </c>
-      <c r="D21" s="7" t="n">
+      <c r="D21" s="5" t="n">
         <v>1950</v>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>STR / RENTAL INCOME</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>216 N. Oak Park Ave</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>APPLIED-YELLOW</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>rent. Dec occupancy vs prepaid? ASK</t>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>APPLIED</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>rent. December occupancy cash. (Half-Nov $975 not on 0203 — WAIT 8507.)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>0203 joint</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>JOAN FRIEDBERGER</t>
         </is>
       </c>
-      <c r="D22" s="7" t="n">
+      <c r="D22" s="5" t="n">
         <v>1950</v>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>STR / RENTAL INCOME</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>216 N. Oak Park Ave</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>APPLIED-YELLOW</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>January rent. Jan 2026 prepaid cash in TY2025. ASK</t>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>APPLIED</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>January rent. Jan 2026 prepaid cash in TY2025.</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Consultant</t>
+          <t>Personal 1099</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>EPGC LLC + GCM</t>
+          <t>GCM tab + Income E7</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>BOM PAYMEN</t>
+          <t>BOM PAYMEN — personal 1099, not EPGC</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Consultant</t>
+          <t>Personal 1099</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>EPGC LLC + GCM</t>
+          <t>GCM tab + Income E7</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>BOM PAYMEN</t>
+          <t>BOM PAYMEN — personal 1099, not EPGC</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Consultant</t>
+          <t>Personal 1099</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>EPGC LLC + GCM</t>
+          <t>GCM tab + Income E7</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>BOM PAYMEN</t>
+          <t>BOM PAYMEN — personal 1099, not EPGC</t>
         </is>
       </c>
     </row>
@@ -1383,12 +1383,12 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Consultant</t>
+          <t>Personal 1099</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>EPGC LLC + GCM</t>
+          <t>GCM tab + Income E7</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
@@ -1398,575 +1398,615 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>BOM PAYMEN</t>
+          <t>BOM PAYMEN — personal 1099, not EPGC</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>9922 JSC</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>2025-02-18</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>Gates Capital</t>
         </is>
       </c>
-      <c r="D27" s="9" t="n">
+      <c r="D27" s="7" t="n">
         <v>1150.99</v>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>Reimbursement</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr">
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>PMT INFO: BOARD MEETING EXPENSES</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>9922 JSC</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>2025-05-22</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>Gates Capital</t>
         </is>
       </c>
-      <c r="D28" s="9" t="n">
+      <c r="D28" s="7" t="n">
         <v>609.02</v>
       </c>
-      <c r="E28" s="8" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>Reimbursement</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G28" s="8" t="inlineStr">
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr">
-        <is>
-          <t>JAKE C — no PMT INFO on statement; odd cents, not BOM — treated as reimburse</t>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>CONFIRMED reimbursement (JAKE C, not BOM)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>9922 JSC</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>2025-11-05</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>Gates Capital</t>
         </is>
       </c>
-      <c r="D29" s="9" t="n">
+      <c r="D29" s="7" t="n">
         <v>1273.82</v>
       </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="E29" s="6" t="inlineStr">
         <is>
           <t>Reimbursement</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G29" s="8" t="inlineStr">
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
         </is>
       </c>
-      <c r="H29" s="8" t="inlineStr">
+      <c r="H29" s="6" t="inlineStr">
         <is>
           <t>Monarch tag Reimburse; statement JAKE C (not BOM)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>8507 NOW (not in folders)</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>8507 NOW (WAIT-MEGAN statements)</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>Gates Capital</t>
         </is>
       </c>
-      <c r="D30" s="9" t="n">
+      <c r="D30" s="7" t="n">
         <v>462.48</v>
       </c>
-      <c r="E30" s="8" t="inlineStr">
+      <c r="E30" s="6" t="inlineStr">
         <is>
           <t>Reimbursement</t>
         </is>
       </c>
-      <c r="F30" s="8" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G30" s="8" t="inlineStr">
+      <c r="G30" s="6" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
         </is>
       </c>
-      <c r="H30" s="8" t="inlineStr">
+      <c r="H30" s="6" t="inlineStr">
         <is>
           <t>SEFOF WHARTON EXPENSES — not on the two BoA folders</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>8507 NOW (not in folders)</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>8507 NOW (WAIT-MEGAN statements)</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>Gates Capital</t>
         </is>
       </c>
-      <c r="D31" s="9" t="n">
+      <c r="D31" s="7" t="n">
         <v>1254.93</v>
       </c>
-      <c r="E31" s="8" t="inlineStr">
+      <c r="E31" s="6" t="inlineStr">
         <is>
           <t>Reimbursement</t>
         </is>
       </c>
-      <c r="F31" s="8" t="inlineStr">
+      <c r="F31" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G31" s="8" t="inlineStr">
+      <c r="G31" s="6" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
         </is>
       </c>
-      <c r="H31" s="8" t="inlineStr">
+      <c r="H31" s="6" t="inlineStr">
         <is>
           <t>SEFOF ANNUAL CONFERENCE EXPENSES</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>8507 NOW (not in folders)</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>8507 NOW (WAIT-MEGAN statements)</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>2025-11-05</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>Gates Capital</t>
         </is>
       </c>
-      <c r="D32" s="9" t="n">
+      <c r="D32" s="7" t="n">
         <v>463.45</v>
       </c>
-      <c r="E32" s="8" t="inlineStr">
+      <c r="E32" s="6" t="inlineStr">
         <is>
           <t>Reimbursement</t>
         </is>
       </c>
-      <c r="F32" s="8" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G32" s="8" t="inlineStr">
+      <c r="G32" s="6" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
         </is>
       </c>
-      <c r="H32" s="8" t="inlineStr">
+      <c r="H32" s="6" t="inlineStr">
         <is>
           <t>SEFOF REIMBURSE EXPENSES FOR EDUCATION COMMITTEE</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>9922 JSC</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>2025-01-09</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>Bear Creek Inc.</t>
         </is>
       </c>
-      <c r="D33" s="9" t="n">
+      <c r="D33" s="7" t="n">
         <v>9500</v>
       </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>Annual gift</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>Annual gift to Jake from parents</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G33" s="8" t="inlineStr">
+      <c r="G33" s="6" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
         </is>
       </c>
-      <c r="H33" s="8" t="inlineStr">
+      <c r="H33" s="6" t="inlineStr">
         <is>
           <t>BEAR CREEK INC - CLIENT W / JPMorgan; PMT DET ATS OF 25/01/07</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>9922 JSC</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>Bear Creek Inc.</t>
         </is>
       </c>
-      <c r="D34" s="9" t="n">
+      <c r="D34" s="7" t="n">
         <v>9500</v>
       </c>
-      <c r="E34" s="8" t="inlineStr">
-        <is>
-          <t>Annual gift</t>
-        </is>
-      </c>
-      <c r="F34" s="8" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>Annual gift to Jake from parents</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G34" s="8" t="inlineStr">
+      <c r="G34" s="6" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
         </is>
       </c>
-      <c r="H34" s="8" t="inlineStr">
+      <c r="H34" s="6" t="inlineStr">
         <is>
           <t>BEAR CREEK INC.-CASH / Northern Trust</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>9922 JSC</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>2025-07-10</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>Bear Creek Inc.</t>
         </is>
       </c>
-      <c r="D35" s="9" t="n">
+      <c r="D35" s="7" t="n">
         <v>9500</v>
       </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>Annual gift</t>
-        </is>
-      </c>
-      <c r="F35" s="8" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>Annual gift to Jake from parents</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G35" s="8" t="inlineStr">
+      <c r="G35" s="6" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
         </is>
       </c>
-      <c r="H35" s="8" t="inlineStr">
+      <c r="H35" s="6" t="inlineStr">
         <is>
           <t>BEAR CREEK INC.-CASH / Northern Trust</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>9922 JSC</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>Bear Creek Inc.</t>
         </is>
       </c>
-      <c r="D36" s="9" t="n">
+      <c r="D36" s="7" t="n">
         <v>9500</v>
       </c>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t>Annual gift</t>
-        </is>
-      </c>
-      <c r="F36" s="8" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>Annual gift to Jake from parents</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G36" s="8" t="inlineStr">
+      <c r="G36" s="6" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
         </is>
       </c>
-      <c r="H36" s="8" t="inlineStr">
+      <c r="H36" s="6" t="inlineStr">
         <is>
           <t>BEAR CREEK INC.-CASH / Northern Trust</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>CMA-Edge 4729</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="C37" s="8" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>THOMAS (wire)</t>
         </is>
       </c>
-      <c r="D37" s="9" t="n">
+      <c r="D37" s="7" t="n">
         <v>5000</v>
       </c>
-      <c r="E37" s="8" t="inlineStr">
+      <c r="E37" s="6" t="inlineStr">
         <is>
           <t>UTMA gift</t>
         </is>
       </c>
-      <c r="F37" s="8" t="inlineStr">
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G37" s="8" t="inlineStr">
+      <c r="G37" s="6" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
         </is>
       </c>
-      <c r="H37" s="8" t="inlineStr">
+      <c r="H37" s="6" t="inlineStr">
         <is>
           <t>WIRE TRF IN ORG THOMAS — Phoebe UTMA (ASK which child)</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>CMA-Edge 2T48</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>THOMAS (wire)</t>
         </is>
       </c>
-      <c r="D38" s="9" t="n">
+      <c r="D38" s="7" t="n">
         <v>5000</v>
       </c>
-      <c r="E38" s="8" t="inlineStr">
+      <c r="E38" s="6" t="inlineStr">
         <is>
           <t>UTMA gift</t>
         </is>
       </c>
-      <c r="F38" s="8" t="inlineStr">
+      <c r="F38" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G38" s="8" t="inlineStr">
+      <c r="G38" s="6" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
         </is>
       </c>
-      <c r="H38" s="8" t="inlineStr">
+      <c r="H38" s="6" t="inlineStr">
         <is>
           <t>WIRE TRF IN ORG THOMAS as-of 11/28 — Emma UTMA 2T48</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>0203 joint</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>2025-12-24</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>Freeman's LLC / CIBC</t>
         </is>
       </c>
-      <c r="D39" s="7" t="n">
+      <c r="D39" s="5" t="n">
         <v>11000</v>
       </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>Unknown — Sale 6428 Contract</t>
-        </is>
-      </c>
-      <c r="F39" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G39" s="6" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="H39" s="6" t="inlineStr">
-        <is>
-          <t>Not payroll. ASK: art sale vs other.</t>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Art-sale settlement Sale 6428</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>Art Sales</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>APPLIED</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>Check to Megan. Sale Price $11,000; Cost / object TBD.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>8507 NOW</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>2025-12-01</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>JOAN FRIEDBERGER</t>
         </is>
       </c>
-      <c r="D40" s="7" t="n">
+      <c r="D40" s="5" t="n">
         <v>-675</v>
       </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>Zelle OUT</t>
-        </is>
-      </c>
-      <c r="F40" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G40" s="6" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="H40" s="6" t="inlineStr">
-        <is>
-          <t>Same day as Joan rent in. Deposit/repair? ASK.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41"/>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>STATUS: APPLIED = in monthly P&amp;L (green). APPLIED-YELLOW = in P&amp;L pending your yes/no. EXCLUDED = not income. HOLD = parked.</t>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>Repair (Zelle OUT)</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>216 INTERIOR MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>APPLIED</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>User: towards a repair. Booked December INTERIOR. Interior vs exterior not specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>8507 NOW</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>JOAN FRIEDBERGER</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>975</v>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>Half-November rent</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>216 N. Oak Park Ave</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>WAIT-MEGAN</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>User: Joan paid half of November. Not on 0203. Do not book until 8507 shows the deposit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>STATUS: APPLIED = in the workbook. EXCLUDED = not income. WAIT-MEGAN = parked until 8507 statements.</t>
         </is>
       </c>
     </row>
